--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-10.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
         <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -775,152 +775,152 @@
         <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
         <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
         <v>3.05</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB2" t="n">
         <v>11</v>
       </c>
-      <c r="AC2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BC2" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.72</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
         <v>5.5</v>
@@ -969,152 +969,152 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
         <v>3.05</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>2.64</v>
@@ -1351,10 +1351,10 @@
         <v>3.25</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
         <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>1.74</v>
       </c>
       <c r="G7" t="n">
         <v>4.8</v>
@@ -1742,7 +1742,7 @@
         <v>2.74</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I11" t="n">
         <v>1.44</v>
@@ -2527,7 +2527,7 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.32</v>
@@ -2548,7 +2548,7 @@
         <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
         <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>21</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="n">
         <v>3.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="R13" t="n">
         <v>1.61</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q21" t="n">
         <v>1.61</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="G22" t="n">
         <v>1.53</v>
@@ -4646,13 +4646,13 @@
         <v>6.8</v>
       </c>
       <c r="I22" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
         <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G23" t="n">
         <v>1.76</v>
@@ -4864,7 +4864,7 @@
         <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G26" t="n">
         <v>1.68</v>
@@ -5422,7 +5422,7 @@
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>3.9</v>
@@ -5446,7 +5446,7 @@
         <v>1.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
         <v>3.25</v>
@@ -5616,13 +5616,13 @@
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J27" t="n">
         <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H28" t="n">
         <v>2.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>3.9</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
         <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>2.12</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I36" t="n">
         <v>4.8</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7747,13 @@
         <v>6.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I38" t="n">
         <v>1.66</v>
       </c>
       <c r="J38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K38" t="n">
         <v>4.6</v>
@@ -7786,7 +7786,7 @@
         <v>1.84</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7795,13 +7795,13 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y38" t="n">
         <v>9.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA38" t="n">
         <v>16.5</v>
@@ -7819,10 +7819,10 @@
         <v>16.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH38" t="n">
         <v>22</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>2.92</v>
       </c>
       <c r="G39" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H39" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J39" t="n">
         <v>3.45</v>
@@ -7992,10 +7992,10 @@
         <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA39" t="n">
         <v>42</v>
@@ -8007,7 +8007,7 @@
         <v>7.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE39" t="n">
         <v>30</v>
@@ -8019,7 +8019,7 @@
         <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI39" t="n">
         <v>50</v>
@@ -8037,7 +8037,7 @@
         <v>100</v>
       </c>
       <c r="AN39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO39" t="n">
         <v>29</v>
@@ -8058,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV39" t="n">
         <v>11</v>
@@ -8076,7 +8076,7 @@
         <v>16.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BB39" t="n">
         <v>40</v>
@@ -8085,20 +8085,20 @@
         <v>29</v>
       </c>
       <c r="BD39" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BE39" t="n">
         <v>80</v>
       </c>
       <c r="BF39" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BG39" t="n">
         <v>24</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G40" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H40" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I40" t="n">
         <v>2.72</v>
@@ -8213,10 +8213,10 @@
         <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ40" t="n">
         <v>40</v>
@@ -8231,10 +8231,10 @@
         <v>70</v>
       </c>
       <c r="AN40" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP40" t="n">
         <v>16.5</v>
@@ -8246,7 +8246,7 @@
         <v>17.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT40" t="n">
         <v>12.5</v>
@@ -8270,7 +8270,7 @@
         <v>13.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BB40" t="n">
         <v>34</v>
@@ -8282,7 +8282,7 @@
         <v>30</v>
       </c>
       <c r="BE40" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF40" t="n">
         <v>17.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR41" t="n">
         <v>34</v>
@@ -8449,7 +8449,7 @@
         <v>8</v>
       </c>
       <c r="AV41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW41" t="n">
         <v>36</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>2.24</v>
       </c>
       <c r="H42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I42" t="n">
         <v>3.95</v>
@@ -8625,10 +8625,10 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
         <v>17.5</v>
@@ -8643,7 +8643,7 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW42" t="n">
         <v>27</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="G43" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K43" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -8905,16 +8905,16 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G44" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H44" t="n">
         <v>2.58</v>
       </c>
       <c r="I44" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J44" t="n">
         <v>3.45</v>
@@ -8938,7 +8938,7 @@
         <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>2.94</v>
       </c>
       <c r="H45" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
         <v>2.56</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -9875,19 +9875,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G49" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H49" t="n">
         <v>1.79</v>
       </c>
       <c r="I49" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="J49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K49" t="n">
         <v>4.7</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.04</v>
       </c>
       <c r="G51" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="H51" t="n">
         <v>1.25</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G59" t="n">
         <v>2.16</v>
@@ -11824,13 +11824,13 @@
         <v>3.65</v>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>3.55</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
         <v>4.7</v>
       </c>
       <c r="I64" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J64" t="n">
         <v>4.2</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -13179,16 +13179,16 @@
         <v>3.05</v>
       </c>
       <c r="H66" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I66" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="J66" t="n">
         <v>3.7</v>
       </c>
       <c r="K66" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -13370,19 +13370,19 @@
         <v>2.24</v>
       </c>
       <c r="G67" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H67" t="n">
         <v>3.15</v>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K67" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -13564,19 +13564,19 @@
         <v>4.4</v>
       </c>
       <c r="G68" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H68" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I68" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>3.85</v>
       </c>
       <c r="K68" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14146,13 +14146,13 @@
         <v>1.97</v>
       </c>
       <c r="G71" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H71" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>3.55</v>
@@ -14173,10 +14173,10 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q73" t="n">
         <v>1.66</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14725,22 +14725,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="H74" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="I74" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="J74" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K74" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H75" t="n">
         <v>3.6</v>
@@ -14949,7 +14949,7 @@
         <v>1.16</v>
       </c>
       <c r="P75" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q75" t="n">
         <v>1.49</v>
@@ -14964,7 +14964,7 @@
         <v>1.5</v>
       </c>
       <c r="U75" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -15501,16 +15501,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G78" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H78" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I78" t="n">
         <v>1.65</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1.66</v>
       </c>
       <c r="J78" t="n">
         <v>4.5</v>
@@ -15543,10 +15543,10 @@
         <v>2.92</v>
       </c>
       <c r="T78" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U78" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y78" t="n">
         <v>9.4</v>
@@ -15564,7 +15564,7 @@
         <v>10.5</v>
       </c>
       <c r="AA78" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB78" t="n">
         <v>22</v>
@@ -15585,7 +15585,7 @@
         <v>22</v>
       </c>
       <c r="AH78" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI78" t="n">
         <v>32</v>
@@ -15600,7 +15600,7 @@
         <v>80</v>
       </c>
       <c r="AM78" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN78" t="n">
         <v>80</v>
@@ -15624,7 +15624,7 @@
         <v>19.5</v>
       </c>
       <c r="AU78" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV78" t="n">
         <v>9.199999999999999</v>
@@ -15633,7 +15633,7 @@
         <v>14.5</v>
       </c>
       <c r="AX78" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AY78" t="n">
         <v>19.5</v>
@@ -15648,23 +15648,23 @@
         <v>80</v>
       </c>
       <c r="BC78" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD78" t="n">
         <v>50</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>48</v>
       </c>
       <c r="BE78" t="n">
         <v>65</v>
       </c>
       <c r="BF78" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BG78" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -15919,10 +15919,10 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
         <v>7.4</v>
       </c>
       <c r="AS81" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT81" t="n">
         <v>16</v>
@@ -16242,11 +16242,11 @@
         <v>46</v>
       </c>
       <c r="BG81" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="G84" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="H84" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J84" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K84" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -16695,10 +16695,10 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17441,19 +17441,19 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="G88" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H88" t="n">
         <v>10.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="K88" t="n">
         <v>1000</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17635,22 +17635,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G89" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H89" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I89" t="n">
         <v>4.3</v>
       </c>
       <c r="J89" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K89" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
         <v>1.6</v>
       </c>
       <c r="H90" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I90" t="n">
         <v>14</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18220,19 +18220,19 @@
         <v>1.59</v>
       </c>
       <c r="G92" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="H92" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="I92" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K92" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18605,22 +18605,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="G94" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="H94" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="I94" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J94" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="K94" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -18635,10 +18635,10 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18799,22 +18799,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="G95" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="H95" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="I95" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J95" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="K95" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -18829,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q95" t="n">
         <v>2.06</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -18993,22 +18993,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="G96" t="n">
         <v>4</v>
       </c>
       <c r="H96" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="I96" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J96" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="K96" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -19023,10 +19023,10 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -19966,16 +19966,16 @@
         <v>1.62</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H101" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I101" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J101" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K101" t="n">
         <v>5</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -20160,13 +20160,13 @@
         <v>1.78</v>
       </c>
       <c r="G102" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H102" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>4.2</v>
@@ -20187,10 +20187,10 @@
         <v>1.25</v>
       </c>
       <c r="P102" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R102" t="n">
         <v>1.49</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -20366,7 +20366,7 @@
         <v>4.1</v>
       </c>
       <c r="K103" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -20381,7 +20381,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q103" t="n">
         <v>1.33</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -20557,7 +20557,7 @@
         <v>4.5</v>
       </c>
       <c r="J104" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K104" t="n">
         <v>3.2</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -20933,10 +20933,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G106" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H106" t="n">
         <v>6.6</v>
@@ -20945,7 +20945,7 @@
         <v>9</v>
       </c>
       <c r="J106" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K106" t="n">
         <v>5.2</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21518,7 @@
         <v>2.16</v>
       </c>
       <c r="G109" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H109" t="n">
         <v>3.75</v>
@@ -21527,7 +21527,7 @@
         <v>3.9</v>
       </c>
       <c r="J109" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K109" t="n">
         <v>3.6</v>
@@ -21536,13 +21536,13 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N109" t="n">
         <v>4.2</v>
       </c>
       <c r="O109" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P109" t="n">
         <v>2.06</v>
@@ -21551,16 +21551,16 @@
         <v>1.88</v>
       </c>
       <c r="R109" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S109" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T109" t="n">
         <v>1.73</v>
       </c>
       <c r="U109" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -21712,10 +21712,10 @@
         <v>3.6</v>
       </c>
       <c r="G110" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H110" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I110" t="n">
         <v>2.16</v>
@@ -21733,13 +21733,13 @@
         <v>1.05</v>
       </c>
       <c r="N110" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O110" t="n">
         <v>1.23</v>
       </c>
       <c r="P110" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q110" t="n">
         <v>1.69</v>
@@ -21754,7 +21754,7 @@
         <v>1.63</v>
       </c>
       <c r="U110" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -21772,7 +21772,7 @@
         <v>17.5</v>
       </c>
       <c r="AA110" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB110" t="n">
         <v>20</v>
@@ -21787,19 +21787,19 @@
         <v>24</v>
       </c>
       <c r="AF110" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG110" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH110" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI110" t="n">
         <v>1000</v>
       </c>
       <c r="AJ110" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK110" t="n">
         <v>48</v>
@@ -21823,7 +21823,7 @@
         <v>10.5</v>
       </c>
       <c r="AR110" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS110" t="n">
         <v>21</v>
@@ -21853,26 +21853,26 @@
         <v>25</v>
       </c>
       <c r="BB110" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC110" t="n">
         <v>32</v>
       </c>
       <c r="BD110" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE110" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF110" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BF110" t="n">
-        <v>5.2</v>
       </c>
       <c r="BG110" t="n">
         <v>10</v>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -21909,10 +21909,10 @@
         <v>3.45</v>
       </c>
       <c r="H111" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J111" t="n">
         <v>3.8</v>
@@ -21933,7 +21933,7 @@
         <v>1.24</v>
       </c>
       <c r="P111" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q111" t="n">
         <v>1.69</v>
@@ -21948,7 +21948,7 @@
         <v>1.64</v>
       </c>
       <c r="U111" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -21978,7 +21978,7 @@
         <v>11.5</v>
       </c>
       <c r="AE111" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF111" t="n">
         <v>27</v>
@@ -22008,7 +22008,7 @@
         <v>28</v>
       </c>
       <c r="AO111" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP111" t="n">
         <v>17</v>
@@ -22029,10 +22029,10 @@
         <v>8</v>
       </c>
       <c r="AV111" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW111" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX111" t="n">
         <v>22</v>
@@ -22047,16 +22047,16 @@
         <v>26</v>
       </c>
       <c r="BB111" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC111" t="n">
         <v>24</v>
       </c>
       <c r="BD111" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE111" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF111" t="n">
         <v>23</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
         <v>5.1</v>
       </c>
       <c r="H112" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I112" t="n">
         <v>1.83</v>
@@ -22121,7 +22121,7 @@
         <v>1.06</v>
       </c>
       <c r="N112" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
         <v>1.28</v>
@@ -22130,19 +22130,19 @@
         <v>2.14</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R112" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S112" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T112" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U112" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -22157,7 +22157,7 @@
         <v>10</v>
       </c>
       <c r="Z112" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA112" t="n">
         <v>21</v>
@@ -22178,22 +22178,22 @@
         <v>44</v>
       </c>
       <c r="AG112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH112" t="n">
         <v>22</v>
       </c>
       <c r="AI112" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ112" t="n">
         <v>1000</v>
       </c>
       <c r="AK112" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL112" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM112" t="n">
         <v>1000</v>
@@ -22208,10 +22208,10 @@
         <v>15</v>
       </c>
       <c r="AQ112" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR112" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS112" t="n">
         <v>16.5</v>
@@ -22220,7 +22220,7 @@
         <v>16</v>
       </c>
       <c r="AU112" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV112" t="n">
         <v>8.800000000000001</v>
@@ -22238,29 +22238,29 @@
         <v>16.5</v>
       </c>
       <c r="BA112" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB112" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC112" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD112" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE112" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF112" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG112" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -22291,13 +22291,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G113" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H113" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I113" t="n">
         <v>6.4</v>
@@ -22315,7 +22315,7 @@
         <v>1.03</v>
       </c>
       <c r="N113" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O113" t="n">
         <v>1.17</v>
@@ -22324,7 +22324,7 @@
         <v>2.76</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R113" t="n">
         <v>1.69</v>
@@ -22396,7 +22396,7 @@
         <v>5.9</v>
       </c>
       <c r="AO113" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP113" t="n">
         <v>24</v>
@@ -22408,7 +22408,7 @@
         <v>6.4</v>
       </c>
       <c r="AS113" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT113" t="n">
         <v>11</v>
@@ -22432,7 +22432,7 @@
         <v>16.5</v>
       </c>
       <c r="BA113" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB113" t="n">
         <v>14</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -22485,22 +22485,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G114" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H114" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I114" t="n">
         <v>3.25</v>
       </c>
       <c r="J114" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K114" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22512,13 +22512,13 @@
         <v>3.5</v>
       </c>
       <c r="O114" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P114" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R114" t="n">
         <v>1.34</v>
@@ -22527,10 +22527,10 @@
         <v>3.3</v>
       </c>
       <c r="T114" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U114" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -22584,10 +22584,10 @@
         <v>46</v>
       </c>
       <c r="AM114" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN114" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO114" t="n">
         <v>1000</v>
@@ -22602,7 +22602,7 @@
         <v>18.5</v>
       </c>
       <c r="AS114" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT114" t="n">
         <v>9.4</v>
@@ -22626,7 +22626,7 @@
         <v>15</v>
       </c>
       <c r="BA114" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB114" t="n">
         <v>25</v>
@@ -22635,20 +22635,20 @@
         <v>19</v>
       </c>
       <c r="BD114" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE114" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF114" t="n">
         <v>19</v>
       </c>
       <c r="BG114" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -22679,13 +22679,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G115" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H115" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I115" t="n">
         <v>2.66</v>
@@ -22703,7 +22703,7 @@
         <v>1.07</v>
       </c>
       <c r="N115" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O115" t="n">
         <v>1.33</v>
@@ -22712,19 +22712,19 @@
         <v>1.96</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R115" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S115" t="n">
         <v>3.55</v>
       </c>
       <c r="T115" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U115" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -22745,7 +22745,7 @@
         <v>1000</v>
       </c>
       <c r="AB115" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC115" t="n">
         <v>8</v>
@@ -22760,10 +22760,10 @@
         <v>22</v>
       </c>
       <c r="AG115" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH115" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI115" t="n">
         <v>42</v>
@@ -22778,19 +22778,19 @@
         <v>1000</v>
       </c>
       <c r="AM115" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN115" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO115" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AP115" t="n">
         <v>12</v>
       </c>
       <c r="AQ115" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR115" t="n">
         <v>14.5</v>
@@ -22799,7 +22799,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT115" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU115" t="n">
         <v>7</v>
@@ -22817,16 +22817,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ115" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA115" t="n">
         <v>34</v>
       </c>
       <c r="BB115" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC115" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD115" t="n">
         <v>9.199999999999999</v>
@@ -22838,11 +22838,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG115" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -22882,13 +22882,13 @@
         <v>16</v>
       </c>
       <c r="I116" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="J116" t="n">
         <v>8.4</v>
       </c>
       <c r="K116" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -22903,16 +22903,16 @@
         <v>1.12</v>
       </c>
       <c r="P116" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R116" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S116" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T116" t="n">
         <v>2</v>
@@ -22954,10 +22954,10 @@
         <v>11</v>
       </c>
       <c r="AG116" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH116" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI116" t="n">
         <v>180</v>
@@ -22972,7 +22972,7 @@
         <v>44</v>
       </c>
       <c r="AM116" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN116" t="n">
         <v>3.05</v>
@@ -22981,16 +22981,16 @@
         <v>1000</v>
       </c>
       <c r="AP116" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR116" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS116" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT116" t="n">
         <v>11.5</v>
@@ -22999,10 +22999,10 @@
         <v>17</v>
       </c>
       <c r="AV116" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW116" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX116" t="n">
         <v>8.199999999999999</v>
@@ -23014,7 +23014,7 @@
         <v>24</v>
       </c>
       <c r="BA116" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB116" t="n">
         <v>9.6</v>
@@ -23026,17 +23026,17 @@
         <v>24</v>
       </c>
       <c r="BE116" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF116" t="n">
         <v>2.7</v>
       </c>
       <c r="BG116" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G118" t="n">
         <v>2.36</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -23464,13 +23464,13 @@
         <v>1.86</v>
       </c>
       <c r="I119" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>3.8</v>
       </c>
       <c r="K119" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -23843,19 +23843,19 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G121" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H121" t="n">
         <v>2.76</v>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J121" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K121" t="n">
         <v>4</v>
@@ -23867,19 +23867,19 @@
         <v>1.04</v>
       </c>
       <c r="N121" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O121" t="n">
         <v>1.22</v>
       </c>
       <c r="P121" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R121" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S121" t="n">
         <v>2.6</v>
@@ -23903,7 +23903,7 @@
         <v>18</v>
       </c>
       <c r="Z121" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA121" t="n">
         <v>55</v>
@@ -23912,10 +23912,10 @@
         <v>16.5</v>
       </c>
       <c r="AC121" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD121" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE121" t="n">
         <v>34</v>
@@ -23927,7 +23927,7 @@
         <v>14.5</v>
       </c>
       <c r="AH121" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI121" t="n">
         <v>40</v>
@@ -23948,7 +23948,7 @@
         <v>17</v>
       </c>
       <c r="AO121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP121" t="n">
         <v>19</v>
@@ -23984,16 +23984,16 @@
         <v>13.5</v>
       </c>
       <c r="BA121" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB121" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD121" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE121" t="n">
         <v>4.9</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -24046,7 +24046,7 @@
         <v>3.55</v>
       </c>
       <c r="I122" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J122" t="n">
         <v>3</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
         <v>2.02</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25398,16 +25398,16 @@
         <v>2.22</v>
       </c>
       <c r="G129" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H129" t="n">
         <v>3.9</v>
       </c>
       <c r="I129" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J129" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K129" t="n">
         <v>3.25</v>
@@ -25558,7 +25558,7 @@
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25592,10 +25592,10 @@
         <v>2.24</v>
       </c>
       <c r="G130" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H130" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I130" t="n">
         <v>3.7</v>
@@ -25752,7 +25752,7 @@
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25783,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G131" t="n">
         <v>1.73</v>
@@ -25792,7 +25792,7 @@
         <v>7</v>
       </c>
       <c r="I131" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J131" t="n">
         <v>3.5</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -25983,7 +25983,7 @@
         <v>4.6</v>
       </c>
       <c r="H132" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I132" t="n">
         <v>2.08</v>
@@ -26140,7 +26140,7 @@
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -26334,7 +26334,7 @@
       </c>
       <c r="BH133" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -26380,7 +26380,7 @@
         <v>3.75</v>
       </c>
       <c r="K134" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -26395,10 +26395,10 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -26528,7 +26528,7 @@
       </c>
       <c r="BH134" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -26722,7 +26722,7 @@
       </c>
       <c r="BH135" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -26916,7 +26916,7 @@
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -27304,7 +27304,7 @@
       </c>
       <c r="BH138" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
@@ -27335,10 +27335,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G139" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H139" t="n">
         <v>4.3</v>
@@ -27347,10 +27347,10 @@
         <v>4.8</v>
       </c>
       <c r="J139" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K139" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -27365,7 +27365,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q139" t="n">
         <v>2.14</v>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="BH139" t="inlineStr">
         <is>
-          <t>2026-05-08 00:37:41</t>
+          <t>2026-05-08 03:10:49</t>
         </is>
       </c>
     </row>
